--- a/AAII_Financials/Quarterly/RITM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RITM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="92">
   <si>
     <t>RITM</t>
   </si>
@@ -656,199 +656,206 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1172800</v>
+        <v>1094000</v>
       </c>
       <c r="E8" s="3">
+        <v>1132900</v>
+      </c>
+      <c r="F8" s="3">
         <v>1146600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>943000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>997600</v>
       </c>
-      <c r="H8" s="3">
-        <v>712700</v>
-      </c>
       <c r="I8" s="3">
+        <v>693300</v>
+      </c>
+      <c r="J8" s="3">
         <v>1251000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>646600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>921300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>891400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>541100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>789600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>972300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>517100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1362700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1929300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1365900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1703000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1045800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>992400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1586900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>883600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>560600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>685000</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>8</v>
+      <c r="D9" s="3">
+        <v>290100</v>
+      </c>
+      <c r="E9" s="3">
+        <v>299400</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>8</v>
@@ -856,11 +863,11 @@
       <c r="G9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>8</v>
+      <c r="H9" s="3">
+        <v>199400</v>
+      </c>
+      <c r="I9" s="3">
+        <v>198500</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>8</v>
@@ -883,112 +890,118 @@
       <c r="P9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R9" s="3">
         <v>283300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>218100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>171800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>164000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>167700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>154200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>271300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>141100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>143100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>153000</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1172800</v>
+        <v>803900</v>
       </c>
       <c r="E10" s="3">
+        <v>833400</v>
+      </c>
+      <c r="F10" s="3">
         <v>1146600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>943000</v>
       </c>
-      <c r="G10" s="3">
-        <v>997600</v>
-      </c>
       <c r="H10" s="3">
-        <v>712700</v>
+        <v>798100</v>
       </c>
       <c r="I10" s="3">
+        <v>494800</v>
+      </c>
+      <c r="J10" s="3">
         <v>1251000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>646600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>921300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>891400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>541100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>789600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>972300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>517100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1079500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1711200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1194100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1539000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>878100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>838200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1315600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>742500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>417500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>532000</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1015,8 +1028,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1089,8 +1103,11 @@
       <c r="Z12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1163,127 +1180,133 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3">
         <v>13900</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
-        <v>18600</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
+        <v>800</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
         <v>-28200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>32900</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>400000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>700</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-1100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-3500</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-100</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>-10100</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>93500</v>
+      </c>
+      <c r="E15" s="3">
         <v>92600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>36000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>23100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>23800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>24600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>24500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>34800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>32900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>32000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>7200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>7100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>7000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>6900</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1311,8 +1334,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1336,156 +1362,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1018500</v>
+        <v>1007100</v>
       </c>
       <c r="E17" s="3">
+        <v>978600</v>
+      </c>
+      <c r="F17" s="3">
         <v>926400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>706100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>691200</v>
       </c>
-      <c r="H17" s="3">
-        <v>655900</v>
-      </c>
       <c r="I17" s="3">
-        <v>739800</v>
+        <v>636500</v>
       </c>
       <c r="J17" s="3">
+        <v>757600</v>
+      </c>
+      <c r="K17" s="3">
         <v>601400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>631100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>538700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>545500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>515800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>529100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>443900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1275000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1753100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1259900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>810300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>828400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>790200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1042600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>484000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>393600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>480300</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>86900</v>
+      </c>
+      <c r="E18" s="3">
         <v>154200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>220200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>236900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>306400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>56800</v>
       </c>
-      <c r="I18" s="3">
-        <v>511200</v>
-      </c>
       <c r="J18" s="3">
+        <v>493400</v>
+      </c>
+      <c r="K18" s="3">
         <v>45100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>290200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>352700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-4400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>273800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>443200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>73100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>87700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>176200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>106000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>892700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>217400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>202200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>544300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>399600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>167000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>204700</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1512,8 +1545,9 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1556,8 +1590,8 @@
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R20" s="3">
         <v>0</v>
@@ -1586,82 +1620,88 @@
       <c r="Z20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>180400</v>
+      </c>
+      <c r="E21" s="3">
         <v>246900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>256200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>260000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>330200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>81300</v>
       </c>
-      <c r="I21" s="3">
-        <v>535700</v>
-      </c>
       <c r="J21" s="3">
+        <v>517900</v>
+      </c>
+      <c r="K21" s="3">
         <v>80000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>323000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>384700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>280900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>450200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>80000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>88500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>179600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>104500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>896800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>220200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>204100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>545600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>400000</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1704,8 +1744,8 @@
       <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1734,156 +1774,165 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>86900</v>
+      </c>
+      <c r="E23" s="3">
         <v>154200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>206300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>236900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>306400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>56800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>492600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>45100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>290200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>380900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-37300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>273800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>443200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>73100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>87800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>176300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>106000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>892700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>217300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>202200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>544200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>399600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>167100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>204700</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E24" s="3">
         <v>44800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>115700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>8100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-11600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-23900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>200700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-78400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>51600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>93400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>29900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>52600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>56500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-16800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-18000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>22100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>72700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>202800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>29500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>31600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>97200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>98300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>65600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>100800</v>
       </c>
     </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1956,156 +2005,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>67900</v>
+      </c>
+      <c r="E26" s="3">
         <v>109500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>90600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>228800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>318000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>80700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>291900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>123600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>238500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>287500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-67200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>221200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>386700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>89900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>105800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>154200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>33300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>689900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>187800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>170700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>447100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>301300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>101500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>103900</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E27" s="3">
         <v>67800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>53100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>193700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>283900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>36500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>263200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>97000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>213200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>261600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-87500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>193900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>357400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>68900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>81800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>124500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-3300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>661900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>160400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>146100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>398900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>277600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>68600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>77900</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2178,8 +2236,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2252,8 +2313,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2326,8 +2390,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2400,8 +2467,11 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2444,8 +2514,8 @@
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R32" s="3">
         <v>0</v>
@@ -2474,82 +2544,88 @@
       <c r="Z32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>56300</v>
+      </c>
+      <c r="E33" s="3">
         <v>102700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>85000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>221500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>311700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>78800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>290200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>121700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>235600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>284000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-65100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>216300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>379800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>91200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>81800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>124500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-3300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>661900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>160400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>146100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>398900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>277600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>68600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>77900</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2622,161 +2698,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>56300</v>
+      </c>
+      <c r="E35" s="3">
         <v>102700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>85000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>221500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>311700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>78800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>290200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>121700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>235600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>284000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-65100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>216300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>379800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>91200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>81800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>124500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-3300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>661900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>160400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>146100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>398900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>277600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>68600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>77900</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2803,8 +2888,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2831,127 +2917,131 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1664500</v>
+      </c>
+      <c r="E41" s="3">
         <v>1646200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1847600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1611000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1600900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1493800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1458700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1639500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1238700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1136400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1287200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1217300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1369000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1434700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1336500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1420000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1510800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1671200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1332600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1366700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>956200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1038500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>944900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>841000</v>
       </c>
     </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>68000</v>
+      </c>
+      <c r="E42" s="3">
         <v>142400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>46700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>53700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>58800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>40600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>75100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>50500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>54400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>102200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1797700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>63500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>55900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>43900</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -2979,82 +3069,88 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5576500</v>
+      </c>
+      <c r="E43" s="3">
         <v>5161400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5185900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4546100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4349200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4310700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4340900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4058100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4329900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4789800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4530700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4674900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4397500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3110400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>639900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>666300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>450000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>738500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>546300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>526700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1829100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>709300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>385000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1120700</v>
       </c>
     </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3097,8 +3193,8 @@
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3127,127 +3223,133 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>7339900</v>
+      </c>
+      <c r="E45" s="3">
         <v>7603400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>7242500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5568200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>5268200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5502600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>6418300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5371900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4956400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4550600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4683300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4485200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3997700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3903400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>60800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>66200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>69900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>83800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>115100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>82000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>41300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>39800</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z45" s="3">
+      <c r="Z45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA45" s="3">
         <v>21800</v>
       </c>
     </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>19816500</v>
+      </c>
+      <c r="E46" s="3">
         <v>20507900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>20748800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>18361200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>16014400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>15100800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>17126400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>14612400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>14787100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>14739700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>15249500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>13628600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>13232500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>11699400</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -3275,230 +3377,242 @@
       <c r="Z46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>15273100</v>
+      </c>
+      <c r="E47" s="3">
         <v>14035000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>13969700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>15906800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>15421600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>17488800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>15991000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>15496800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>14968900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>16240400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>13255200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>10649100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>10142900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>9457100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>28652000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>31440200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>30892400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>33491800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>35832100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>37392900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>33122200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>32341700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>30850600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>27451200</v>
       </c>
     </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>183200</v>
+      </c>
+      <c r="E48" s="3">
         <v>191100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>206100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>183000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>179400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>180000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>169700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>172000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>142400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>135700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>144200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>104400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>110900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>115400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>115200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>123600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>143300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>160800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>173700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>175200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>53400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>56300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>26900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>54500</v>
       </c>
     </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>12072100</v>
+      </c>
+      <c r="E49" s="3">
         <v>11859800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>11369300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>11154800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>11146300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>10940700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>11156600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>10150800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10585700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>9462700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>9196900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>9186300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>9196200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>9409700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>226600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>232000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>230900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>227900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>228300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>103200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>61600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>62800</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z49" s="3">
+      <c r="Z49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA49" s="3">
         <v>64500</v>
       </c>
     </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3571,8 +3685,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3645,82 +3762,88 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6757800</v>
+      </c>
+      <c r="E52" s="3">
         <v>6774500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>6762800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1559400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1554200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1619700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1605300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1843900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1251700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1257500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1592200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1177200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1175600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1137000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>281100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>529600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>434000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>295000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>195900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>194700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>238500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>136000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>135600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>230100</v>
       </c>
     </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3793,82 +3916,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>54108900</v>
+      </c>
+      <c r="E54" s="3">
         <v>53374500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>53063100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>47165400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>44316000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>45329800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>46049000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>42276000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>42018900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>42120900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>39717100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>34745500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>33858100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>31818700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>32479300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>35334500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>34553800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>37868500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>39742200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>41604100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>37250400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>35184100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>33252100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>30406400</v>
       </c>
     </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3895,8 +4024,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3923,275 +4053,285 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>281100</v>
+      </c>
+      <c r="E57" s="3">
         <v>324200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>294400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>700100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>148100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>127400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>133000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>180100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>201500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1389400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>165100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>178000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>189800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>160800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>886700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>685700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>199900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>226900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>316700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>331700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>123500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>104100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>97000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>129900</v>
       </c>
     </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>19768200</v>
+        <v>13333200</v>
       </c>
       <c r="E58" s="3">
-        <v>19206900</v>
+        <v>15340600</v>
       </c>
       <c r="F58" s="3">
+        <v>15254100</v>
+      </c>
+      <c r="G58" s="3">
         <v>18439200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>19345800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>19815600</v>
       </c>
-      <c r="I58" s="3">
-        <v>12682400</v>
-      </c>
       <c r="J58" s="3">
+        <v>9936700</v>
+      </c>
+      <c r="K58" s="3">
         <v>819400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>422800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1059900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>9191900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>11807600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>10695800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>9264200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>11257700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>13655200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>13967200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>17281900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>20592900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>22760000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>21290900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>19522500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>17547700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>14666900</v>
       </c>
     </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>192400</v>
+        <v>4502800</v>
       </c>
       <c r="E59" s="3">
-        <v>196700</v>
+        <v>4620100</v>
       </c>
       <c r="F59" s="3">
+        <v>4149500</v>
+      </c>
+      <c r="G59" s="3">
         <v>2869900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2425600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2590000</v>
       </c>
-      <c r="I59" s="3">
-        <v>153100</v>
-      </c>
       <c r="J59" s="3">
+        <v>2898900</v>
+      </c>
+      <c r="K59" s="3">
         <v>2560400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2044600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1981600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3746200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1610000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1455400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1321900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>436300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>706500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>642600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>665900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>648200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1127500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>446000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>696400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>404200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>390900</v>
       </c>
     </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>18543500</v>
+      </c>
+      <c r="E60" s="3">
         <v>20610300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>20313800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>22410000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>22292600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>22872700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>13552500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3958000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3015100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4687100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>13560300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>13921700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>12562500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>10936200</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -4219,142 +4359,148 @@
       <c r="Z60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>23294100</v>
+      </c>
+      <c r="E61" s="3">
         <v>20433900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>20844300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>14544700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>12474400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>13025700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>23222900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>29373100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>30034400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>28647000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>17814800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>12420100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>13039500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>12927600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>10644000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>10198300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>9866200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>9823300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>9188100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>8790900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>7846400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>7649800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>8185700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>8275400</v>
       </c>
     </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1910600</v>
+      </c>
+      <c r="E62" s="3">
         <v>1926000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1791500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>554700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>482300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>530100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>583800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>583900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>567500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>606400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>401600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>337500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>310000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>305300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>711900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>738200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>716100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>642000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>440700</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>8</v>
       </c>
@@ -4367,8 +4513,11 @@
       <c r="Z62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4441,8 +4590,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4515,8 +4667,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4589,82 +4744,88 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>44660100</v>
+      </c>
+      <c r="E66" s="3">
         <v>43869200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>43808400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>38255900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>35995800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>37188600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>38162600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>34524600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>34598300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>34877600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>32616000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>27477600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>26663400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>24864100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>25536300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>28344000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>27560000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>30745900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>33138200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>35048000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>31178300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>29661300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>27931100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>25077200</v>
       </c>
     </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4691,8 +4852,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4765,8 +4927,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4839,8 +5004,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4848,19 +5016,19 @@
         <v>1632900</v>
       </c>
       <c r="E70" s="3">
-        <v>1390800</v>
+        <v>1632900</v>
       </c>
       <c r="F70" s="3">
         <v>1390800</v>
       </c>
       <c r="G70" s="3">
-        <v>1207300</v>
+        <v>1390800</v>
       </c>
       <c r="H70" s="3">
         <v>1207300</v>
       </c>
       <c r="I70" s="3">
-        <v>1257300</v>
+        <v>1207300</v>
       </c>
       <c r="J70" s="3">
         <v>1257300</v>
@@ -4887,7 +5055,7 @@
         <v>1257300</v>
       </c>
       <c r="R70" s="3">
-        <v>1258700</v>
+        <v>1257300</v>
       </c>
       <c r="S70" s="3">
         <v>1258700</v>
@@ -4896,13 +5064,13 @@
         <v>1258700</v>
       </c>
       <c r="U70" s="3">
-        <v>1262500</v>
+        <v>1258700</v>
       </c>
       <c r="V70" s="3">
         <v>1262500</v>
       </c>
       <c r="W70" s="3">
-        <v>813000</v>
+        <v>1262500</v>
       </c>
       <c r="X70" s="3">
         <v>813000</v>
@@ -4913,8 +5081,11 @@
       <c r="Z70" s="3">
         <v>813000</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>813000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4987,82 +5158,88 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-226400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-100000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-19900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>70800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>18400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-129900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-47000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-177700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-143200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-232100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-373100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-164000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-236200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-470600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-418700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-381800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-387900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-267900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-813000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-856800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-886300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-914300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-1108900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-1094600</v>
       </c>
     </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5135,8 +5312,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5209,8 +5389,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5283,82 +5466,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6883900</v>
+      </c>
+      <c r="E76" s="3">
         <v>6977200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7039700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7107700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6741100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6568900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6537700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6399300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6069300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5892300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5749700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5950800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5877200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5637000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>5685700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>5731900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>5735200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>5864000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>5341600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>5293600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>5259100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4709800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4508000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4516200</v>
       </c>
     </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5431,161 +5620,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>56300</v>
+      </c>
+      <c r="E81" s="3">
         <v>102700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>85000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>221500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>311700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>78800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>290200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>121700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>235600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>284000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-65100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>216300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>379800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>91200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>81800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>124500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-3300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>661900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>160400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>146100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>398900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>277600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>68600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>77900</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5612,82 +5810,86 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E83" s="3">
         <v>24600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>11700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>10200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>9400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>13000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>7200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>7100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>7000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>6900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>6500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>5800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4100</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
       <c r="R83" s="3">
         <v>0</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T83" s="3">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+      <c r="T83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U83" s="3">
         <v>4100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>2900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>400</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5760,8 +5962,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5834,8 +6039,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5908,8 +6116,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5982,8 +6193,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6056,82 +6270,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>174100</v>
+      </c>
+      <c r="E89" s="3">
         <v>100700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-114600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2041700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-557100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1421300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1753400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>768100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>114600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1314500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1046900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>509000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>50300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1181300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>142200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1376600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1465100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3890200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>3570400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>320100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-1006600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-495300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-29900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-880400</v>
       </c>
     </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6158,8 +6378,9 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6202,38 +6423,41 @@
       <c r="P91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="Q91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R91" s="3">
         <v>-19100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-42000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-115700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-239300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-472500</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
-      <c r="W91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X91" s="3">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-72400</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6306,8 +6530,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6380,82 +6607,88 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1234100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-739500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>1449100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>625600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>1901200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1304500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-337600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-676200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>2638900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4050200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>1707700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-639000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-261400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-590600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>1052800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1319900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>1201700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-736300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-500800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>5181200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2374100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-798500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2322300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-5395500</v>
       </c>
     </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6482,8 +6715,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6526,38 +6760,41 @@
       <c r="P96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="Q96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R96" s="3">
         <v>-118600</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-118400</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-116700</v>
       </c>
       <c r="T96" s="3">
         <v>-116700</v>
       </c>
       <c r="U96" s="3">
+        <v>-116700</v>
+      </c>
+      <c r="V96" s="3">
         <v>-116600</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-93300</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-165900</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-82900</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-62400</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-41600</v>
       </c>
     </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6630,8 +6867,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6704,8 +6944,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6778,82 +7021,88 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1135600</v>
+      </c>
+      <c r="E100" s="3">
         <v>312300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-790900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1510900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1283800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>56000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2005400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>349800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2749800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>5225600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-556800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>25500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>96800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-408000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1526900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-51900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-2688200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-2716100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-3102600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-5134600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>3495000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1387900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>2411100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>6145400</v>
       </c>
     </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6896,8 +7145,8 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -6926,78 +7175,84 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>75600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-326400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>543600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>94900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>60300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>172800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-85600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>441700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>3700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-139100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>104000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-104500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-114400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>182700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-331900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>4800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-21400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>437800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-33000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>366700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>114300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>94000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>58900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-130600</v>
       </c>
     </row>
